--- a/data/trans_orig/Predimed_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según adherencia a la dieta mediterránea en 2023</t>
+          <t>Población según adherencia a la dieta mediterránea en 2023 (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>103494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142496</t>
+          <t>144042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122272</t>
+          <t>124923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155798</t>
+          <t>158584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>234645</t>
+          <t>235511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285088</t>
+          <t>287739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>434219</t>
+          <t>432673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>473890</t>
+          <t>473221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>471097</t>
+          <t>468311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>504623</t>
+          <t>501972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>918523</t>
+          <t>915872</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>968966</t>
+          <t>968100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65274</t>
+          <t>70647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177793</t>
+          <t>179226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132276</t>
+          <t>131794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168875</t>
+          <t>171189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174950</t>
+          <t>190065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>332173</t>
+          <t>333981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>940963</t>
+          <t>939530</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1053482</t>
+          <t>1048109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>718433</t>
+          <t>716119</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755032</t>
+          <t>755514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1673890</t>
+          <t>1672082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1831113</t>
+          <t>1815998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92370</t>
+          <t>92416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135693</t>
+          <t>135660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71746</t>
+          <t>74011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228981</t>
+          <t>225219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161398</t>
+          <t>169737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337523</t>
+          <t>336177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506879</t>
+          <t>506912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550202</t>
+          <t>550156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656891</t>
+          <t>660653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>814126</t>
+          <t>811861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1190921</t>
+          <t>1192267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1367046</t>
+          <t>1358707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131233</t>
+          <t>130758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>175145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160405</t>
+          <t>159139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227915</t>
+          <t>228027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>310824</t>
+          <t>305341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389770</t>
+          <t>390088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>710220</t>
+          <t>713174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>757086</t>
+          <t>757561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>833736</t>
+          <t>833624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>901246</t>
+          <t>902512</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1560200</t>
+          <t>1559882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1639146</t>
+          <t>1644629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390986</t>
+          <t>396623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>577176</t>
+          <t>579041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>727904</t>
+          <t>721511</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>990921</t>
+          <t>986434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1266726</t>
+          <t>1258894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2649186</t>
+          <t>2647321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2835376</t>
+          <t>2829739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2733822</t>
+          <t>2740215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2946526</t>
+          <t>2946594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5421362</t>
+          <t>5429194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5697167</t>
+          <t>5701654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>134714</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103494</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144042</t>
+          <t>158357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>139475</t>
+          <t>149597</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124923</t>
+          <t>131275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158584</t>
+          <t>168034</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>260361</t>
+          <t>284310</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235511</t>
+          <t>261454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>287739</t>
+          <t>317804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>455829</t>
+          <t>491295</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432673</t>
+          <t>467652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>473221</t>
+          <t>511350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>487420</t>
+          <t>527912</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>468311</t>
+          <t>509475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>501972</t>
+          <t>546234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>943250</t>
+          <t>1019207</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>915872</t>
+          <t>985713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>968100</t>
+          <t>1042063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>576715</t>
+          <t>626009</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>576715</t>
+          <t>626009</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>576715</t>
+          <t>626009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>626895</t>
+          <t>677509</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>626895</t>
+          <t>677509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>626895</t>
+          <t>677509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1203611</t>
+          <t>1303517</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1203611</t>
+          <t>1303517</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1203611</t>
+          <t>1303517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>131485</t>
+          <t>151821</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70647</t>
+          <t>129345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179226</t>
+          <t>178553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>149876</t>
+          <t>168365</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131794</t>
+          <t>147337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171189</t>
+          <t>190147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>281361</t>
+          <t>320186</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190065</t>
+          <t>289011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>333981</t>
+          <t>354317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>987271</t>
+          <t>818072</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>939530</t>
+          <t>791340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1048109</t>
+          <t>840548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>737432</t>
+          <t>824838</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>716119</t>
+          <t>803056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755514</t>
+          <t>845866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1724702</t>
+          <t>1642910</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1672082</t>
+          <t>1608779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1815998</t>
+          <t>1674085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1118756</t>
+          <t>969893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1118756</t>
+          <t>969893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1118756</t>
+          <t>969893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>887308</t>
+          <t>993203</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>887308</t>
+          <t>993203</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>887308</t>
+          <t>993203</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2006063</t>
+          <t>1963096</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2006063</t>
+          <t>1963096</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2006063</t>
+          <t>1963096</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>111267</t>
+          <t>127078</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92416</t>
+          <t>105130</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>150870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>145998</t>
+          <t>136809</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74011</t>
+          <t>118032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225219</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>257265</t>
+          <t>263888</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169737</t>
+          <t>235937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>336177</t>
+          <t>294379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>531305</t>
+          <t>602386</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506912</t>
+          <t>578594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550156</t>
+          <t>624334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>739874</t>
+          <t>621025</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>660653</t>
+          <t>600861</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>811861</t>
+          <t>639802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1271179</t>
+          <t>1223410</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1192267</t>
+          <t>1192919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1358707</t>
+          <t>1251361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>642572</t>
+          <t>729464</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>642572</t>
+          <t>729464</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>642572</t>
+          <t>729464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>885872</t>
+          <t>757834</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>885872</t>
+          <t>757834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>885872</t>
+          <t>757834</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1528444</t>
+          <t>1487298</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1528444</t>
+          <t>1487298</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1528444</t>
+          <t>1487298</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>152880</t>
+          <t>163862</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130758</t>
+          <t>139760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175145</t>
+          <t>189063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>199969</t>
+          <t>209416</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159139</t>
+          <t>188114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228027</t>
+          <t>234121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>352849</t>
+          <t>373278</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305341</t>
+          <t>342180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390088</t>
+          <t>406944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>735439</t>
+          <t>788064</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>713174</t>
+          <t>762863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>757561</t>
+          <t>812166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>861682</t>
+          <t>873592</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>833624</t>
+          <t>848887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>902512</t>
+          <t>894894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,22 +1937,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1597121</t>
+          <t>1661656</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1559882</t>
+          <t>1627990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1644629</t>
+          <t>1692754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>888319</t>
+          <t>951926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>888319</t>
+          <t>951926</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>888319</t>
+          <t>951926</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1061651</t>
+          <t>1083008</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1061651</t>
+          <t>1083008</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1061651</t>
+          <t>1083008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1949970</t>
+          <t>2034934</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1949970</t>
+          <t>2034934</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1949970</t>
+          <t>2034934</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>516519</t>
+          <t>577475</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>396623</t>
+          <t>533687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>579041</t>
+          <t>631365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>635318</t>
+          <t>664187</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>515132</t>
+          <t>625674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>721511</t>
+          <t>707948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1151836</t>
+          <t>1241662</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>986434</t>
+          <t>1175345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1258894</t>
+          <t>1310511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2709843</t>
+          <t>2699816</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2647321</t>
+          <t>2645926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2829739</t>
+          <t>2743604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2826408</t>
+          <t>2847367</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2740215</t>
+          <t>2803606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2946594</t>
+          <t>2885880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5536252</t>
+          <t>5547183</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5429194</t>
+          <t>5478334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5701654</t>
+          <t>5613500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3226362</t>
+          <t>3277291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3461726</t>
+          <t>3511554</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6688088</t>
+          <t>6788845</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
